--- a/submit_template.xlsx
+++ b/submit_template.xlsx
@@ -1,59 +1,543 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="22192" windowHeight="10455"/>
   </bookViews>
   <sheets>
-    <sheet name="Papers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Papers" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
+  <si>
+    <t>doi</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>authors</t>
+  </si>
+  <si>
+    <t>publish date</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>summary motivation</t>
+  </si>
+  <si>
+    <t>summary innovation</t>
+  </si>
+  <si>
+    <t>summary method</t>
+  </si>
+  <si>
+    <t>summary conclusion</t>
+  </si>
+  <si>
+    <t>summary limitation</t>
+  </si>
+  <si>
+    <t>paper url</t>
+  </si>
+  <si>
+    <t>project url</t>
+  </si>
+  <si>
+    <t>conference</t>
+  </si>
+  <si>
+    <t>title translation</t>
+  </si>
+  <si>
+    <t>analogy summary</t>
+  </si>
+  <si>
+    <t>pipeline figure</t>
+  </si>
+  <si>
+    <t>abstract</t>
+  </si>
+  <si>
+    <t>contributor</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>10.48550/arXiv.2407.07061</t>
+  </si>
+  <si>
+    <t>Internet of agents: Weaving a web of heterogeneous agents for collaborative intelligence</t>
+  </si>
+  <si>
+    <t>Weize Chen*, Ziming You*, Ran Li*, Yitong Guan*, Chen Qian, Chenyang Zhao Cheng Yang, Ruobing Xie, Zhiyuan Liu, Maosong Sun</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>Base Techniques</t>
+  </si>
+  <si>
+    <t>先前的multi-agent系统的局限性，系统化平台化程度不足（缺乏第三方集成支持，无法分布式，通信协议和状态转换依赖于硬编码）</t>
+  </si>
+  <si>
+    <t>将互联网的开放、分布式、服务化思想引入，构建一种标准化、可扩展的支持分布式、异构的智能体集成与通信协议。</t>
+  </si>
+  <si>
+    <t>服务器：智能体注册（分发系统提示词）、管理已注册智能体（专家）、专家发现服务、群聊管理和消息传递；客户端：包装具体智能体，提供通信接口；三层结构；通信即可嵌套灵活群聊；群聊采用**有限状态机**管理流程；平台初始化与注册-&gt;任务触发团队形成-&gt;内部嵌套协作</t>
+  </si>
+  <si>
+    <t>在 GAIA 基准测试中，仅使用四个基础 ReAct 智能体即达到最佳性能；在 RAG 任务中，基于 GPT-3.5 的 IoA 达到或超过 GPT-4 的性能</t>
+  </si>
+  <si>
+    <t>实验中存在冗余消息，通信 Token 消耗增加近一倍，这证明agent作为对话者而非执行者的本质能力区别；单点服务器可能存在瓶颈；智能体通过注册获取提示词成为不同专家，仍高度依赖人工实验设计，且这种专家的能力是否可靠</t>
+  </si>
+  <si>
+    <t>https://openreview.net/forum?id=o1Et3MogPw</t>
+  </si>
+  <si>
+    <t>https://github.com/OpenBMB/IoA</t>
+  </si>
+  <si>
+    <t>The Thirteenth International Conference on Learning Representations</t>
+  </si>
+  <si>
+    <t>[AI generated] **智能体互联网：构建异构智能体网络以实现协同智能**
+**说明：**
+1.  **核心概念直译**：将 "Internet of Agents" 直译为“智能体互联网”，准确对应其借鉴互联网理念的核心创新，并与物联网（IoT）等术语形成概念类比，符合学术语境。
+2.  **副标题意译与优化**：将 "Weaving a web of heterogeneous agents for collaborative intelligence" 意译为“构建异构智能体网络</t>
+  </si>
+  <si>
+    <t>agent互联网，升级版ABM系统，采用类似互联网思想，C/S架构，分布化、服务化、平台化</t>
+  </si>
+  <si>
+    <t>figures/IoA.png;figures/IoA2.png</t>
+  </si>
+  <si>
+    <t>The rapid advancement of large language models (LLMs) has paved the way for the development of highly capable autonomous agents. However, existing multi-agent frameworks often struggle with integrating diverse capable third-party agents due to reliance on agents defined within their own ecosystems. They also face challenges in simulating distributed environments, as most frameworks are limited to single-device setups. Furthermore, these frameworks often rely on hard-coded communication pipelines, limiting their adaptability to dynamic task requirements. Inspired by the concept of the Internet, we propose the Internet of Agents (IoA), a novel framework that addresses these limitations by providing a flexible and scalable platform for LLM-based multi-agent collaboration. IoA introduces an agent integration protocol, an instant-messaging-like architecture design, and dynamic mechanisms for agent teaming and conversation flow control. Through extensive experiments on general assistant tasks, embodied AI tasks, and retrieval-augmented generation benchmarks, we demonstrate that IoA consistently outperforms state-of-the-art baselines, showcasing its ability to facilitate effective collaboration among heterogeneous agents. IoA represents a step towards linking diverse agents in an Internet-like environment, where agents can seamlessly collaborate to achieve greater intelligence and capabilities. We will release our code to facilitate further research.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>每个agent被一个客户端包装；服务器不是agent，它只做四件事：注册、发现、建群、路由；相对于传统ABM，这是一个更大型的服务系统，该方法通过基于任务的“群聊”方式组织问题解决，相对传统回合制方式更加自由。本身也是一个高度可扩展系统。问题在于智能体通过注册获取提示词成为不同专家，仍依赖手工设计，且这种专家的能力是否可靠。对于社会模拟任务相对于传统方法有何决定性优势仍未可知</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
-    <fill>
-      <patternFill/>
+  <fills count="35">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EEFF"/>
-        <bgColor rgb="00D9EEFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000B66C3"/>
-        <bgColor rgb="000B66C3"/>
+        <fgColor rgb="FF0B66C3"/>
+        <bgColor rgb="FF0B66C3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EEFF"/>
+        <bgColor rgb="FFD9EEFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -62,96 +546,334 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -434,138 +1156,156 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
+    <col min="1" max="5" width="15" customWidth="1"/>
+    <col min="6" max="7" width="21" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="10" width="21" customWidth="1"/>
+    <col min="11" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="16" width="18" customWidth="1"/>
+    <col min="17" max="19" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>doi</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>authors</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>publish date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>summary motivation</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>summary innovation</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>summary method</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>summary conclusion</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>summary limitation</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>paper url</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>project url</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>conference</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>title translation</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>analogy summary</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>pipeline figure</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>abstract</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>contributor</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
+    <row r="1" spans="1:24">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:24">
+      <c r="A2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>